--- a/string_pair_dataset.xlsx
+++ b/string_pair_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pappu\OneDrive\Desktop\BTP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DFA8440-16D7-44C9-9ECE-6B23BCD5ECAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA77A72C-E051-44E8-9CB6-63C8A3168FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8582,7 +8582,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.77734375" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
